--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Shared\DocumentsValidationData\Passing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn5\Shared\DocumentsValidationData\Passing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1506A6E2-E885-4AD2-A531-20F7B150DBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0014B6F-94E5-42C6-B5D0-F8BB0AE30DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33765" yWindow="-1500" windowWidth="21600" windowHeight="12780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6501" uniqueCount="975">
   <si>
     <t>Source</t>
   </si>
@@ -6718,7 +6718,9 @@
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
       <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
+      <c r="X7" s="46" t="s">
+        <v>136</v>
+      </c>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
       <c r="AA7" s="54"/>
@@ -6768,7 +6770,9 @@
       <c r="U8" s="20"/>
       <c r="V8" s="20"/>
       <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
+      <c r="X8" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
       <c r="AA8" s="54"/>
